--- a/results/Int Task Remove ACC 0.8/Rando_3_permute.xlsx
+++ b/results/Int Task Remove ACC 0.8/Rando_3_permute.xlsx
@@ -440,347 +440,347 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7490707701457033</v>
+        <v>0.7451494201605708</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7490707701457033</v>
+        <v>0.7440529289325007</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7472680642283676</v>
+        <v>0.7440529289325007</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7483645554564378</v>
+        <v>0.7440529289325007</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7446848052334225</v>
+        <v>0.7349278917633065</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7464875111507583</v>
+        <v>0.7349278917633065</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7457441272673209</v>
+        <v>0.7349278917633065</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7443688670829616</v>
+        <v>0.7349278917633065</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7443688670829616</v>
+        <v>0.7349278917633065</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7443688670829616</v>
+        <v>0.7338314005352364</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7423431460005947</v>
+        <v>0.7334782931906036</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7418785310734464</v>
+        <v>0.7292038358608386</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7418785310734464</v>
+        <v>0.7292038358608386</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7352995837050252</v>
+        <v>0.7306534344335415</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7312667261373773</v>
+        <v>0.7287763901278621</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6803635147190008</v>
+        <v>0.7284232827832293</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6705694320547131</v>
+        <v>0.7306162652393695</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6617975022301517</v>
+        <v>0.7306162652393695</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.653378679750223</v>
+        <v>0.7291294974724949</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6562778768956289</v>
+        <v>0.7291294974724949</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6606638418079096</v>
+        <v>0.719614183764496</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6522821885221528</v>
+        <v>0.7214540588760036</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6522821885221528</v>
+        <v>0.7123661909009813</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.439804490038656</v>
+        <v>0.7112696996729111</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4397673208444841</v>
+        <v>0.7205248290217068</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4401204281891169</v>
+        <v>0.7176999702646447</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4387079988105858</v>
+        <v>0.7118644067796611</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.4387079988105858</v>
+        <v>0.7240559024680344</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.4387079988105858</v>
+        <v>0.696940975319655</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.4319617900683913</v>
+        <v>0.6958444840915849</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4326680047576568</v>
+        <v>0.6486210228962237</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4340432649420161</v>
+        <v>0.6486210228962237</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.4195658638120726</v>
+        <v>0.5164659530181386</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.4192127564674398</v>
+        <v>0.5164659530181386</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4153285756764794</v>
+        <v>0.5154438001784121</v>
       </c>
     </row>
     <row r="37">
@@ -790,37 +790,37 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.415997621171573</v>
+        <v>0.5084002378828427</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4099947963128159</v>
+        <v>0.499423877490336</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4187853107344633</v>
+        <v>0.5016168599464764</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4188224799286351</v>
+        <v>0.4881058578650015</v>
       </c>
     </row>
     <row r="41">
@@ -830,293 +830,293 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.439804490038656</v>
+        <v>0.4774197145405888</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4327423431460006</v>
+        <v>0.4774197145405888</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4193986024382991</v>
+        <v>0.4727178114778471</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4254757656854</v>
+        <v>0.4733125185845971</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4247695509961344</v>
+        <v>0.4808392804044008</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4191198334820101</v>
+        <v>0.513473832887303</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4138232233125186</v>
+        <v>0.5141800475765685</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4148825453464169</v>
+        <v>0.5010964912280702</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4148825453464169</v>
+        <v>0.4967105263157895</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4265722569134701</v>
+        <v>0.4920086232530479</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4273156407969075</v>
+        <v>0.4920086232530479</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4339875111507582</v>
+        <v>0.50516651798989</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4568651501635445</v>
+        <v>0.5007805530776093</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4522004162949748</v>
+        <v>0.5070621468926554</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4546721677074042</v>
+        <v>0.5070621468926554</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4447851620576866</v>
+        <v>0.5036239964317574</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4590395480225989</v>
+        <v>0.4905218554861731</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4593926553672316</v>
+        <v>0.4890722569134701</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4625706214689266</v>
+        <v>0.4862473981564079</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.475635593220339</v>
+        <v>0.4897413024085638</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4964689265536723</v>
+        <v>0.4886076419863217</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4971751412429379</v>
+        <v>0.4878642581028844</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4978813559322034</v>
+        <v>0.4893138566755872</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4989406779661017</v>
+        <v>0.4871580434136188</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4996468926553672</v>
+        <v>0.4971565566458519</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4996468926553672</v>
+        <v>0.4975096639904847</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4992937853107345</v>
+        <v>0.5024531668153435</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4992937853107345</v>
+        <v>0.5024531668153435</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4985875706214689</v>
+        <v>0.4997584002378828</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -1126,187 +1126,187 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4982344632768362</v>
+        <v>0.4989406779661017</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4982344632768362</v>
+        <v>0.4989406779661017</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4985875706214689</v>
+        <v>0.4992937853107345</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4996468926553672</v>
+        <v>0.4989406779661017</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4996468926553672</v>
+        <v>0.4992937853107345</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4996468926553672</v>
+        <v>0.5003902765388046</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4996468926553672</v>
+        <v>0.5003902765388046</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5</v>
+        <v>0.5007433838834374</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5</v>
+        <v>0.5007433838834374</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5</v>
+        <v>0.5007433838834374</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5</v>
+        <v>0.4990150163544455</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5</v>
+        <v>0.4986619090098127</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5</v>
+        <v>0.4990150163544455</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5</v>
+        <v>0.4990150163544455</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5</v>
+        <v>0.4983088016651799</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5</v>
+        <v>0.4983088016651799</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5</v>
+        <v>0.4993309545049063</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5</v>
+        <v>0.4989778471602735</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B89" t="n">
